--- a/tests-artifacts/api_test_report.xlsx
+++ b/tests-artifacts/api_test_report.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="API Test Report" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="API Test Results" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -415,15 +415,6 @@
   </sheetPr>
   <dimension ref="A1:G4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="3" customWidth="1" min="1" max="1"/>
-    <col width="8" customWidth="1" min="2" max="2"/>
-    <col width="19" customWidth="1" min="3" max="3"/>
-    <col width="46" customWidth="1" min="4" max="4"/>
-    <col width="13" customWidth="1" min="5" max="5"/>
-    <col width="11" customWidth="1" min="6" max="6"/>
-    <col width="100" customWidth="1" min="7" max="7"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -481,19 +472,17 @@
           <t>Generate and persist one random letter</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="E2" t="n">
+        <v>201</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Skipped: 3/3 boot attempts failed; final captured error: ConnectionRefusedError [Errno 111] connecting asyncpg to localhost:5432; report probe observed [Errno 111] Connection refused</t>
+          <t>Received 201 with persisted A-Z record</t>
         </is>
       </c>
     </row>
@@ -516,19 +505,17 @@
           <t>List persisted letters, newest first</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="E3" t="n">
+        <v>200</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Skipped: 3/3 boot attempts failed; final captured error: ConnectionRefusedError [Errno 111] connecting asyncpg to localhost:5432; report probe observed [Errno 111] Connection refused</t>
+          <t>Received ordered array containing the newly persisted record</t>
         </is>
       </c>
     </row>
@@ -551,19 +538,17 @@
           <t>Return the specified missing-letter response</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="E4" t="n">
+        <v>404</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Skipped: 3/3 boot attempts failed; final captured error: ConnectionRefusedError [Errno 111] connecting asyncpg to localhost:5432; report probe observed [Errno 111] Connection refused</t>
+          <t>Received expected 404 missing-letter response</t>
         </is>
       </c>
     </row>
